--- a/output/version_scores.xlsx
+++ b/output/version_scores.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1406,7 +1406,376 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>output/eval_runs/v3set_sf_v3_p2_20261011-020946</t>
+          <t>output/eval_runs/v3set_sf_v3_p2_attr_20261011-120349</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ 跨语言 xlang=dict</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>retrieval-only；中文题 Hit@1 85.0%→76.1%，不默认</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_xl_dict_20261011-122759</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ 跨语言 xlang=auto 门控</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>retrieval-only；MRR 0.893→0.888，中性，不默认</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_xl_auto_20261011-132112</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【v3·检索】Contextual 前缀集合</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>heading_v2_ctx max800</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>retrieval-only；MRR 0.890，中性，不默认</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_ctx_20261011-125125</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ 多查询 multiq=rule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>retrieval-only；MRR 0.852，退步，不默认</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_mq_rule_20261011-130020</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【v3 子集22题·本地3B】p1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>子集=难题（V3 漏写/检索失败）+P05/P13/P15/O03；规则 v3</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>output/eval_runs/rf3b_p1_20261011-132414</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【v3 子集22题·本地3B】p3 要点先行</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>output/eval_runs/rf3b_p3_20261011-133403</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【v3 子集22题·本地3B】p3 + reflect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>自检+补检1轮</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>output/eval_runs/rf3b_p3_reflect_20261011-134700</t>
         </is>
       </c>
     </row>

--- a/output/version_scores.xlsx
+++ b/output/version_scores.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1779,6 +1779,273 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【v3·139题】云 V3 + p3 要点先行</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>检索复用 p2 基线；自动评分持平，人工抽查 15 道变化题净 +5；未设默认</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3set_sf_v3_p3_20261011-154227</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【v3·139题】云 V3 + p3 + reflect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="P25" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5 题触发补检；费用 ≈1.8×；未设默认</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3set_sf_v3_p3_reflect_20261011-160820</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ V3 翻译 xlang=llm（权重0.7）</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="P26" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>retrieval-only；中文 MRR 0.904→0.878，退步</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_xl_v3llm_20261011-162333</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ V3 翻译 mismatch 门控</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>retrieval-only；中性</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_xl_v3mismatch_20261011-163118</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【v3·检索】+ V3 翻译 cap 30% ★云端默认</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>heading_v2 max800</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>retrieval-only；MRR 0.896，中文持平；跨语言 36 题 MRR 0.657→0.745</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>output/eval_runs/v3_xl_v3cap_20261011-164218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
